--- a/Sindhi Muslim/Weekly Diary/Weekly Diary - 23-11-2024.xlsx
+++ b/Sindhi Muslim/Weekly Diary/Weekly Diary - 23-11-2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Weekly Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C4659B-ED73-4765-9626-65AE0D3E8993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037BFDEC-8A35-48AC-9E03-AE3672295C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{AC0A426B-C469-4DBE-A695-5879DF716B89}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{AC0A426B-C469-4DBE-A695-5879DF716B89}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (ROSE)" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="31">
   <si>
     <t>Date</t>
   </si>
@@ -85,28 +85,12 @@
     <t>Do Home Work Page No# 63, 64</t>
   </si>
   <si>
-    <t>Months Name
-Aug-Sep-Oct-Nov-Dec</t>
-  </si>
-  <si>
-    <t>حروفِ تہجی
-ا سے ص تک یاد کریں</t>
-  </si>
-  <si>
     <t>Table of 3</t>
   </si>
   <si>
-    <t>Name of Months
-Jan-Dec</t>
-  </si>
-  <si>
     <t>دنوں کے نام یاد کریں</t>
   </si>
   <si>
-    <t>Number in Words
-1-10</t>
-  </si>
-  <si>
     <t>Do Home Work Page No# 69, 70</t>
   </si>
   <si>
@@ -132,6 +116,18 @@
   </si>
   <si>
     <t>Number Counting 1-30</t>
+  </si>
+  <si>
+    <t>حروفِ تہجی (ا سے ص تک یاد کریں)</t>
+  </si>
+  <si>
+    <t>Number in Words (1-10)</t>
+  </si>
+  <si>
+    <t>Name of Months (Jan-Dec)</t>
+  </si>
+  <si>
+    <t>Months Name (Aug-Sep-Oct-Nov-Dec)</t>
   </si>
 </sst>
 </file>
@@ -144,13 +140,6 @@
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -171,18 +160,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="36"/>
-      <color theme="1"/>
-      <name val="Algerian"/>
-      <family val="5"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
     </font>
   </fonts>
   <fills count="2">
@@ -420,7 +416,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -435,7 +431,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -450,7 +446,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -459,85 +455,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,325 +856,905 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A70CFE-6773-48B7-8C4D-649243C54D39}">
-  <dimension ref="A1:E9"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
+    </row>
+    <row r="3" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>45621</v>
+      </c>
+      <c r="B4" s="15" t="str">
+        <f>TEXT(A4,"dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B5" s="5" t="str">
+        <f t="shared" ref="B5:B9" si="0">TEXT(A5,"dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>Friday</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="8" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="10">
+        <v>45626</v>
+      </c>
+      <c r="B9" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+    </row>
+    <row r="13" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>45621</v>
+      </c>
+      <c r="B14" s="15" t="str">
+        <f>TEXT(A14,"dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" ref="B15:B19" si="1">TEXT(A15,"dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B18" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Friday</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>45626</v>
+      </c>
+      <c r="B19" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+    </row>
+    <row r="23" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>45621</v>
+      </c>
+      <c r="B24" s="15" t="str">
+        <f>TEXT(A24,"dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B25" s="5" t="str">
+        <f t="shared" ref="B25:B29" si="2">TEXT(A25,"dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B26" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B27" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B28" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Friday</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10">
+        <v>45626</v>
+      </c>
+      <c r="B29" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A11:E12"/>
+    <mergeCell ref="A21:E22"/>
+    <mergeCell ref="A1:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="91" fitToWidth="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0712DE0C-E31D-4B31-BC62-DEFC64633194}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-    </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="4" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
         <v>45621</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" s="5" t="str">
         <f>TEXT(A4,"dddd")</f>
         <v>Monday</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="C4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
         <v>45622</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B5" s="5" t="str">
         <f t="shared" ref="B5:B9" si="0">TEXT(A5,"dddd")</f>
         <v>Tuesday</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
         <v>45623</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Wednesday</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
         <v>45624</v>
       </c>
-      <c r="B7" s="1" t="str">
+      <c r="B7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Thursday</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
         <v>45625</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Friday</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>23</v>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="8" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="10">
         <v>45626</v>
       </c>
-      <c r="B9" s="9" t="str">
+      <c r="B9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Saturday</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="11" t="s">
+      <c r="D9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+    </row>
+    <row r="13" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>45621</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f>TEXT(A14,"dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="15" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f t="shared" ref="B15:B19" si="1">TEXT(A15,"dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B16" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B17" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B18" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>Friday</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="8" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="10">
+        <v>45626</v>
+      </c>
+      <c r="B19" s="11" t="str">
+        <f t="shared" si="1"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+    </row>
+    <row r="23" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>45621</v>
+      </c>
+      <c r="B24" s="5" t="str">
+        <f>TEXT(A24,"dddd")</f>
+        <v>Monday</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B25" s="5" t="str">
+        <f t="shared" ref="B25:B29" si="2">TEXT(A25,"dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B26" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B27" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Thursday</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="8" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A28" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B28" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>Friday</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="8" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="10">
+        <v>45626</v>
+      </c>
+      <c r="B29" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>Saturday</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A21:E22"/>
     <mergeCell ref="A1:E2"/>
+    <mergeCell ref="A11:E12"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0712DE0C-E31D-4B31-BC62-DEFC64633194}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-    </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>45621</v>
-      </c>
-      <c r="B4" s="1" t="str">
-        <f>TEXT(A4,"dddd")</f>
-        <v>Monday</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>45622</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <f t="shared" ref="B5:B9" si="0">TEXT(A5,"dddd")</f>
-        <v>Tuesday</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>45623</v>
-      </c>
-      <c r="B6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Wednesday</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>45624</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Thursday</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>45625</v>
-      </c>
-      <c r="B8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>Friday</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
-        <v>45626</v>
-      </c>
-      <c r="B9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v>Saturday</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>